--- a/news_daily/2026-09-15.xlsx
+++ b/news_daily/2026-09-15.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1169,6 +1197,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1339,6 +1371,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1389,13 +1425,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1444,7 +1484,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>42ead0dbf58a426c800d79a939cd9c2d</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>aeb45096162290b28c99814b</t>
@@ -1465,7 +1509,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1509,176 +1557,216 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Connecticut Medicaid program to receive $936K from Abbott Laboratories settlement</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPS05OUnRwQWJkM21KM2NfaGpxemlqQ3NhSGxlcy1kV0g5M0RqdUx4LTVwdEFGdzJoUHVoX3FoMzNvMk1WVUxFeUk3YjhWQWJjbWNVTWxmOW5OOXZSRS03ZFF3bmFRalpVMGJmbDJjaGRDazNqX3c0MlpzTU1YdW4tMmM2X3Y4VXBkLUtfbEVRSnktWTZ5UFlLY3JBcHBtbjczWkFsNWhFLVVNeXJIUWJncmFOS01GOXh3dDA1M21oa0VVd185MU5mWlF0MXVvU2ZMNHg5aDlpaEVzTWY4VkVXT0pwLUFIV09CY3FVRnpXRmVUbGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>fox61.com</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>a119d1cb78e143cfb45d8742997a4328</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>62506c2d9c83d9d0656f4594</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>ec21bbb73be47802577ac901</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.884</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPS05OUnRwQWJkM21KM2NfaGpxemlqQ3NhSGxlcy1kV0g5M0RqdUx4LTVwdEFGdzJoUHVoX3FoMzNvMk1WVUxFeUk3YjhWQWJjbWNVTWxmOW5OOXZSRS03ZFF3bmFRalpVMGJmbDJjaGRDazNqX3c0MlpzTU1YdW4tMmM2X3Y4VXBkLUtfbEVRSnktWTZ5UFlLY3JBcHBtbjczWkFsNWhFLVVNeXJIUWJncmFOS01GOXh3dDA1M21oa0VVd185MU5mWlF0MXVvU2ZMNHg5aDlpaEVzTWY4VkVXT0pwLUFIV09CY3FVRnpXRmVUbGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>fox61.com</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>62506c2d9c83d9d0656f4594</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>ec21bbb73be47802577ac901</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1849,6 +1937,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1889,7 +1981,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1899,13 +1991,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1945,7 +2041,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1954,7 +2050,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>09c772e23e14468a8ffecdb9f1956231</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>b7d9f9ead8da1a1b8075887e</t>
@@ -1975,7 +2075,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2019,6 +2123,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2181,6 +2301,10 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2231,13 +2355,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2286,7 +2414,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>9ec0fd2aa8c64969b0573a48ab9fa4fd</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>f6156f7dfecd4bae5f9fd382</t>
@@ -2307,7 +2439,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2351,6 +2487,18 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2401,13 +2549,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2456,7 +2608,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>c5be8f4ac06b47e6af9ae2897b1cea55</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>f16c57f4e4ccdbc3d0fb01d2</t>
@@ -2477,7 +2633,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2521,6 +2681,18 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2691,6 +2863,10 @@
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2731,7 +2907,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2741,13 +2917,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2787,7 +2967,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2796,7 +2976,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>a50e73500f66419c996e2c43ee1ca8ba</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>8937f4792f33fa34b473a6e2</t>
@@ -2817,7 +3001,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2853,6 +3041,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3023,6 +3227,10 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr"/>
+      <c r="BL14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3193,6 +3401,10 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3363,9 +3575,13 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH16"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3376,7 +3592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3439,6 +3655,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3742,6 +3962,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3792,13 +4032,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -3847,7 +4091,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>42ead0dbf58a426c800d79a939cd9c2d</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>aeb45096162290b28c99814b</t>
@@ -3868,7 +4116,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -3912,6 +4164,18 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3941,7 +4205,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Connecticut Medicaid program to receive $936K from Abbott Laboratories settlement</t>
+          <t>Abbott Laboratories (ABT) Agrees To $385 Million Infant Formula Recall Settlement</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -3952,7 +4216,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3962,13 +4226,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -3978,7 +4246,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>'-0.308</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -3992,12 +4260,12 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPS05OUnRwQWJkM21KM2NfaGpxemlqQ3NhSGxlcy1kV0g5M0RqdUx4LTVwdEFGdzJoUHVoX3FoMzNvMk1WVUxFeUk3YjhWQWJjbWNVTWxmOW5OOXZSRS03ZFF3bmFRalpVMGJmbDJjaGRDazNqX3c0MlpzTU1YdW4tMmM2X3Y4VXBkLUtfbEVRSnktWTZ5UFlLY3JBcHBtbjczWkFsNWhFLVVNeXJIUWJncmFOS01GOXh3dDA1M21oa0VVd185MU5mWlF0MXVvU2ZMNHg5aDlpaEVzTWY4VkVXT0pwLUFIV09CY3FVRnpXRmVUbGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaGpsOERFV1VYNXF0ck4wS3VwNl9xVEtXRnJ5ZFJYYkN5NVAzSlZJREdPcG1TZjlpU2JrNWVtNnFfZkJWaGhnaGhvcl9CRDFlaHFjZDRuQWRPeGR2azlBcTR3T2J6a19COU5MVHVrakRXdGl1S01Md3dOUTJKYWlMenFqbGEwdXBHNkJFRlBLWWpqN0RQajFTMnR1NA?oc=5</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>fox61.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr"/>
@@ -4008,7 +4276,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -4017,15 +4285,19 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>09c772e23e14468a8ffecdb9f1956231</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>62506c2d9c83d9d0656f4594</t>
+          <t>b7d9f9ead8da1a1b8075887e</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>ec21bbb73be47802577ac901</t>
+          <t>fccbde31663f926dc0ddc4af</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr"/>
@@ -4038,7 +4310,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -4082,338 +4358,382 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories (ABT) Agrees To $385 Million Infant Formula Recall Settlement</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Goldman Sachs might be warming up for some more job cuts soon</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>'-0.308</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.816</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaGpsOERFV1VYNXF0ck4wS3VwNl9xVEtXRnJ5ZFJYYkN5NVAzSlZJREdPcG1TZjlpU2JrNWVtNnFfZkJWaGhnaGhvcl9CRDFlaHFjZDRuQWRPeGR2azlBcTR3T2J6a19COU5MVHVrakRXdGl1S01Md3dOUTJKYWlMenFqbGEwdXBHNkJFRlBLWWpqN0RQajFTMnR1NA?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>b7d9f9ead8da1a1b8075887e</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>fccbde31663f926dc0ddc4af</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPa2hHdWtKdWpPSWVPZEVrOTA5Y0NkM2ZxenFZR1A3NlRDUTEyZktpemtlUUQ2d1NjODhVT05SYXFCemhnSm9YRW9fdmNwQW1kOEdUY2NiZEFJRnMwTEZzQzlmdVd5STFWb3FOWnZnVENWQjRLM2F2a20xdWxWY1hNSnJCbTU0ZFRtSC10LTBZZU40SVhSUURMeWwwZHRHR1lUSGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>eFinancialCareers</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>e18ea88ffeb7b32d16bbd37d</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>3271abc8dd42797c2ec52a2f</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr"/>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs might be warming up for some more job cuts soon</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Accenture (ACN) Agrees To $25 Million DOJ Discrimination Settlement</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>0.757</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOFpqak5pdWprWi1fNE9LckF5OVhmSVlvOXdYaWI2S0VacUp4M0xwcXlYSy1fYl8wZ2szTVRDbmN4SG5jQ1dja2NwVUpQSWE4clgyQWIySDN3NWFXdlFvSXJOWkRkUWtIWTl5Y196UTZCbVBZSzlSd0hUcjNCenFfUVVZVzA2Ui16NE9zeGlubENNTDkyMWozYjMxaXE?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>9ec0fd2aa8c64969b0573a48ab9fa4fd</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>f6156f7dfecd4bae5f9fd382</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>a190b9ecbdbb850881d2bb0a</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>'-0.816</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPa2hHdWtKdWpPSWVPZEVrOTA5Y0NkM2ZxenFZR1A3NlRDUTEyZktpemtlUUQ2d1NjODhVT05SYXFCemhnSm9YRW9fdmNwQW1kOEdUY2NiZEFJRnMwTEZzQzlmdVd5STFWb3FOWnZnVENWQjRLM2F2a20xdWxWY1hNSnJCbTU0ZFRtSC10LTBZZU40SVhSUURMeWwwZHRHR1lUSGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>eFinancialCareers</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>e18ea88ffeb7b32d16bbd37d</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>3271abc8dd42797c2ec52a2f</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4443,7 +4763,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Accenture (ACN) Agrees To $25 Million DOJ Discrimination Settlement</t>
+          <t>Justice extracts $25M settlement from Accenture Federal over diversity goals</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -4464,13 +4784,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -4480,7 +4804,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>'-0.816</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
@@ -4494,12 +4818,12 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOFpqak5pdWprWi1fNE9LckF5OVhmSVlvOXdYaWI2S0VacUp4M0xwcXlYSy1fYl8wZ2szTVRDbmN4SG5jQ1dja2NwVUpQSWE4clgyQWIySDN3NWFXdlFvSXJOWkRkUWtIWTl5Y196UTZCbVBZSzlSd0hUcjNCenFfUVVZVzA2Ui16NE9zeGlubENNTDkyMWozYjMxaXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNTGdKSjJqSXVOdlNQMGhRUU5pRzVPNDhmak9NODk5eURvdWVWVUZDWUQyZ0FubUxBU2ZTMlhhNXdmNXpxWkp5ZTg5Z253c3A2U05SeUIzOG5ubmlwcHRLNTNPWFBIbWtuN3d6NEUxY3EzMVcyRk5VaW9tRUR6YzBQd0FqU0JUTE9EMTZPUGdXLUdmODhYYUtUVzJTam96dmx1bE94Vl9ya0xzaFhlVjhhUDktaDc1R2RRTTFOQ2pFd3pNTTJTbG0yQjgyTzhCUQ?oc=5</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Washington Technology</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr"/>
@@ -4519,15 +4843,19 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>c5be8f4ac06b47e6af9ae2897b1cea55</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>f6156f7dfecd4bae5f9fd382</t>
+          <t>f16c57f4e4ccdbc3d0fb01d2</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>a190b9ecbdbb850881d2bb0a</t>
+          <t>3f8e678737ec3625d5fea794</t>
         </is>
       </c>
       <c r="AE6" s="3" t="inlineStr"/>
@@ -4540,7 +4868,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -4584,681 +4916,559 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PepsiCo, Inc.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Justice extracts $25M settlement from Accenture Federal over diversity goals</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Job cuts at PepsiCo facility in Cheverly</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.816</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.954</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNTGdKSjJqSXVOdlNQMGhRUU5pRzVPNDhmak9NODk5eURvdWVWVUZDWUQyZ0FubUxBU2ZTMlhhNXdmNXpxWkp5ZTg5Z253c3A2U05SeUIzOG5ubmlwcHRLNTNPWFBIbWtuN3d6NEUxY3EzMVcyRk5VaW9tRUR6YzBQd0FqU0JUTE9EMTZPUGdXLUdmODhYYUtUVzJTam96dmx1bE94Vl9ya0xzaFhlVjhhUDktaDc1R2RRTTFOQ2pFd3pNTTJTbG0yQjgyTzhCUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Washington Technology</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>f16c57f4e4ccdbc3d0fb01d2</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>3f8e678737ec3625d5fea794</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOVEpfQ0lWbm1Lb1UyWHB1VGN3ZFNnUm9BOV9lamVxclhVeDFweEJfdDdrYVF4NmpMZXFrRWx2SEpXc0k2Wjl4OW1JaUlHWklTTkR5ZjFIMXZTNjBpb0JVOGVSeDFMYjBFTUhtUi1KWXBwY2w4ZXJlOHlzdzdxcFdjRjNEZXd0RnhWUE5qcTZCS2VqU1lDVDZuYWFheGl6am4yOTBUYWt3N2haRzJNRjFSR2pMOFIwNGJCOWtCUlFfTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>wusa9.com</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>f1b134fae37bfd768515d420</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>3c55a9054e5f9458c85b7c79</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>PepsiCo, Inc.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Job cuts at PepsiCo facility in Cheverly</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Judge Sets Date For Settlement Talks In Paramount-WBD Antitrust Case</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>'-0.008</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOMjkwNkdDVHdJODRRR0FwX21nendxQ2lYdGVDSldpWUlCNFBFcFZfeEcxbmR1dHpoUVZnaDNmcE1ROGtNLWU5Yng3MlRrNWQxZlBTOXNaQW45WnNRdEprSko2djJ2Y1g5YVFzT3pKLUZfbUJLNWE1RXlfbGlpeW5VNXRIaktMOUpHV0t6Ynl1ZTFOUEM0VlNWM3htM0I?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>a50e73500f66419c996e2c43ee1ca8ba</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>8937f4792f33fa34b473a6e2</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>a138928f5f0609c6962c6200</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.954</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOVEpfQ0lWbm1Lb1UyWHB1VGN3ZFNnUm9BOV9lamVxclhVeDFweEJfdDdrYVF4NmpMZXFrRWx2SEpXc0k2Wjl4OW1JaUlHWklTTkR5ZjFIMXZTNjBpb0JVOGVSeDFMYjBFTUhtUi1KWXBwY2w4ZXJlOHlzdzdxcFdjRjNEZXd0RnhWUE5qcTZCS2VqU1lDVDZuYWFheGl6am4yOTBUYWt3N2haRzJNRjFSR2pMOFIwNGJCOWtCUlFfTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>wusa9.com</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>f1b134fae37bfd768515d420</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>3c55a9054e5f9458c85b7c79</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Copart, Inc.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Judge Sets Date For Settlement Talks In Paramount-WBD Antitrust Case</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>How Copart’s (CPRT) Slower EPS and Margin Compression Has Changed Its Investment Story</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.008</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOMjkwNkdDVHdJODRRR0FwX21nendxQ2lYdGVDSldpWUlCNFBFcFZfeEcxbmR1dHpoUVZnaDNmcE1ROGtNLWU5Yng3MlRrNWQxZlBTOXNaQW45WnNRdEprSko2djJ2Y1g5YVFzT3pKLUZfbUJLNWE1RXlfbGlpeW5VNXRIaktMOUpHV0t6Ynl1ZTFOUEM0VlNWM3htM0I?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>8937f4792f33fa34b473a6e2</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>a138928f5f0609c6962c6200</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSVJTZ0RRb3NZX2M5NmNNV0dWem04OEpBUEFCbGZqbGZPdmFiODFPa25pZ2ZLbktzNW0yTEdXQU4tR0ZELW9RUkR1UktmbHJjZlEzcWlXM3VGOXQtSUhFeHRrajJnVlhLWFJvQUdSN2pqeWxFcHk0VTFHMTB1T0ZjS190cl82NUZTNS1QNVRxbzNtcWZRcEhTX2l3?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>margin compression</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>8ad443fd9bd9de27595a8293</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>57964828f90fa7454fc5fa7b</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Copart, Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>How Copart’s (CPRT) Slower EPS and Margin Compression Has Changed Its Investment Story</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSVJTZ0RRb3NZX2M5NmNNV0dWem04OEpBUEFCbGZqbGZPdmFiODFPa25pZ2ZLbktzNW0yTEdXQU4tR0ZELW9RUkR1UktmbHJjZlEzcWlXM3VGOXQtSUhFeHRrajJnVlhLWFJvQUdSN2pqeWxFcHk0VTFHMTB1T0ZjS190cl82NUZTNS1QNVRxbzNtcWZRcEhTX2l3?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>margin compression</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>8ad443fd9bd9de27595a8293</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>57964828f90fa7454fc5fa7b</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5269,7 +5479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5332,6 +5542,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5635,9 +5849,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5648,7 +5882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5711,6 +5945,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6014,9 +6252,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6027,7 +6285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6077,134 +6335,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -6214,46 +6472,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6262,12 +6554,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6277,90 +6569,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6370,94 +6666,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6465,89 +6761,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-15.xlsx
+++ b/news_daily/2026-09-15.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -2189,13 +2189,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2244,7 +2248,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>a690c8466f08472f9e449adc24e80f73</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>e18ea88ffeb7b32d16bbd37d</t>
@@ -2265,7 +2273,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2303,8 +2315,16 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2743,13 +2763,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -2798,7 +2822,11 @@
         </is>
       </c>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>bde92a128f3640c5a04e63533e188d1c</t>
+        </is>
+      </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>f1b134fae37bfd768515d420</t>
@@ -2819,7 +2847,11 @@
       <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="inlineStr"/>
       <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="inlineStr"/>
@@ -2865,8 +2897,16 @@
       <c r="BH12" s="4" t="inlineStr"/>
       <c r="BI12" s="4" t="inlineStr"/>
       <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3059,178 +3099,202 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Copart, Inc.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-09-15T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>How Copart’s (CPRT) Slower EPS and Margin Compression Has Changed Its Investment Story</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSVJTZ0RRb3NZX2M5NmNNV0dWem04OEpBUEFCbGZqbGZPdmFiODFPa25pZ2ZLbktzNW0yTEdXQU4tR0ZELW9RUkR1UktmbHJjZlEzcWlXM3VGOXQtSUhFeHRrajJnVlhLWFJvQUdSN2pqeWxFcHk0VTFHMTB1T0ZjS190cl82NUZTNS1QNVRxbzNtcWZRcEhTX2l3?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>margin compression</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>99dee7b576a743969f3c3c0215c0a191</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>8ad443fd9bd9de27595a8293</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>57964828f90fa7454fc5fa7b</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSVJTZ0RRb3NZX2M5NmNNV0dWem04OEpBUEFCbGZqbGZPdmFiODFPa25pZ2ZLbktzNW0yTEdXQU4tR0ZELW9RUkR1UktmbHJjZlEzcWlXM3VGOXQtSUhFeHRrajJnVlhLWFJvQUdSN2pqeWxFcHk0VTFHMTB1T0ZjS190cl82NUZTNS1QNVRxbzNtcWZRcEhTX2l3?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>margin compression</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>8ad443fd9bd9de27595a8293</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>57964828f90fa7454fc5fa7b</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="BC14" s="4" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="4" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="4" t="inlineStr">
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr"/>
-      <c r="BL14" s="4" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL9"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4424,13 +4488,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -4479,7 +4547,11 @@
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>a690c8466f08472f9e449adc24e80f73</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>e18ea88ffeb7b32d16bbd37d</t>
@@ -4500,7 +4572,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -4538,8 +4614,16 @@
       <c r="BH4" s="4" t="inlineStr"/>
       <c r="BI4" s="4" t="inlineStr"/>
       <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4978,13 +5062,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -5033,7 +5121,11 @@
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>bde92a128f3640c5a04e63533e188d1c</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>f1b134fae37bfd768515d420</t>
@@ -5054,7 +5146,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -5100,8 +5196,16 @@
       <c r="BH7" s="4" t="inlineStr"/>
       <c r="BI7" s="4" t="inlineStr"/>
       <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5293,182 +5397,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Copart, Inc.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>How Copart’s (CPRT) Slower EPS and Margin Compression Has Changed Its Investment Story</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSVJTZ0RRb3NZX2M5NmNNV0dWem04OEpBUEFCbGZqbGZPdmFiODFPa25pZ2ZLbktzNW0yTEdXQU4tR0ZELW9RUkR1UktmbHJjZlEzcWlXM3VGOXQtSUhFeHRrajJnVlhLWFJvQUdSN2pqeWxFcHk0VTFHMTB1T0ZjS190cl82NUZTNS1QNVRxbzNtcWZRcEhTX2l3?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>margin compression</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>8ad443fd9bd9de27595a8293</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>57964828f90fa7454fc5fa7b</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr"/>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL9"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-15.xlsx
+++ b/news_daily/2026-09-15.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>e80d7e9f56114e418bf593e22ae7a798</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>83df377af17259e436da96a1</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1023,10 +1035,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1062,28 +1086,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1123,7 +1151,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1132,7 +1160,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>b48ef1adae314a64a9ba7e6a8b366c28</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>bc08122c50f1953c2d0c2236</t>
@@ -1153,7 +1185,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1197,10 +1233,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1236,28 +1284,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1297,7 +1349,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1306,7 +1358,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>63c89edd1ff742cf9e487dcc4fabdaae</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>b28b7412769056b833e0c8cd</t>
@@ -1327,7 +1383,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1371,10 +1431,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1802,28 +1874,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1863,7 +1939,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1872,7 +1948,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>61daf84a7d6c4b55afcbec0336e4d67c</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>d8dc4800b4571ec2ef2ba32e</t>
@@ -1893,7 +1973,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1937,10 +2021,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3345,13 +3441,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3400,7 +3500,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>a40a1abc882146c28023db784dc90891</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>3a2fef6391edd58defe31a02</t>
@@ -3421,7 +3525,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3467,8 +3575,16 @@
       <c r="BH15" s="2" t="inlineStr"/>
       <c r="BI15" s="2" t="inlineStr"/>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3519,13 +3635,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3574,7 +3694,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>709a4c95bd214fa29f784cb6402c1f52</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>3853a39a500dd4338650c75e</t>
@@ -3595,7 +3719,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3641,8 +3769,16 @@
       <c r="BH16" s="2" t="inlineStr"/>
       <c r="BI16" s="2" t="inlineStr"/>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL16"/>
